--- a/outputs/3939-kanamic-valuation.xlsx
+++ b/outputs/3939-kanamic-valuation.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="3939_valuation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3939_valuation" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,19 +49,19 @@
       <color rgb="00000000"/>
     </font>
     <font>
+      <color rgb="001F4E78"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="001F4E78"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="001F4E78"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-    </font>
-    <font>
-      <color rgb="001F4E78"/>
-      <sz val="11"/>
-    </font>
-    <font>
       <color rgb="001F4E78"/>
     </font>
   </fonts>
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -154,19 +154,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,7 +169,7 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -255,14 +249,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -286,7 +280,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -306,11 +300,11 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'3939_valuation'!A31</f>
+              <f>'3939_valuation'!A32</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -321,7 +315,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'3939_valuation'!$B$31:$I$31</f>
+              <f>'3939_valuation'!$B$32:$I$32</f>
             </numRef>
           </val>
         </ser>
@@ -330,11 +324,11 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'3939_valuation'!A46</f>
+              <f>'3939_valuation'!A48</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -345,7 +339,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'3939_valuation'!$B$46:$I$46</f>
+              <f>'3939_valuation'!$B$48:$I$48</f>
             </numRef>
           </val>
         </ser>
@@ -364,7 +358,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -372,7 +366,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -396,8 +390,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -423,8 +417,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -449,8 +443,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -477,14 +471,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -508,7 +502,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -538,7 +532,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -546,7 +540,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -570,8 +564,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -597,8 +591,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -623,8 +617,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -651,19 +645,19 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>セグメント別売上(積上げ視覚)</a:t>
+              <a:t>セグメント別売上</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -682,7 +676,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -706,7 +700,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -730,7 +724,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -760,7 +754,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -768,7 +762,7 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -792,8 +786,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -819,8 +813,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -845,8 +839,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -873,14 +867,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -900,11 +894,11 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'3939_valuation'!A73</f>
+              <f>'3939_valuation'!A75</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -915,7 +909,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'3939_valuation'!$B$73:$I$73</f>
+              <f>'3939_valuation'!$B$75:$I$75</f>
             </numRef>
           </val>
         </ser>
@@ -930,11 +924,11 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'3939_valuation'!A74</f>
+              <f>'3939_valuation'!A76</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -942,14 +936,14 @@
             <symbol val="circle"/>
             <size val="7"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <val>
             <numRef>
-              <f>'3939_valuation'!$B$74:$I$74</f>
+              <f>'3939_valuation'!$B$76:$I$76</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -966,8 +960,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -993,8 +987,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1019,8 +1013,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -1047,7 +1041,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -1062,9 +1056,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1084,9 +1078,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1106,9 +1100,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1128,9 +1122,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1428,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1516,35 +1510,42 @@
           <t>売上高 合計</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>3746</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>5007</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>5501</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>6350</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>7200</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>6500</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>8100</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>10100</v>
+      <c r="B3" s="7">
+        <f>B7+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>C7+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D3" s="7">
+        <f>D7+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E3" s="7">
+        <f>E7+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F3" s="7">
+        <f>F7+F11+F12</f>
+        <v/>
+      </c>
+      <c r="G3" s="7">
+        <f>G7+G11+G12</f>
+        <v/>
+      </c>
+      <c r="H3" s="7">
+        <f>H7+H11+H12</f>
+        <v/>
+      </c>
+      <c r="I3" s="7">
+        <f>I7+I11+I12</f>
+        <v/>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>連結損益計算書(FY23-25実績)、FY26は会社予想(2026年5月13日決算説明資料)、FY27/FY28はストーリーmd</t>
-        </is>
+      <c r="K3" s="5">
+        <f>セグメント3区分の合計。FY23のクラウドPF事業内訳は健康寿命延伸を控除した値</f>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -1554,26 +1555,29 @@
         </is>
       </c>
       <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>0.134</v>
+      <c r="C4" s="9">
+        <f>C3/B3-1</f>
+        <v/>
+      </c>
+      <c r="D4" s="9">
+        <f>D3/C3-1</f>
+        <v/>
+      </c>
+      <c r="E4" s="9">
+        <f>E3/D3-1</f>
+        <v/>
+      </c>
+      <c r="F4" s="9">
+        <f>F3/E3-1</f>
+        <v/>
       </c>
       <c r="G4" s="9" t="n"/>
       <c r="H4" s="9" t="n"/>
       <c r="I4" s="9" t="n"/>
       <c r="J4" s="10" t="inlineStr"/>
-      <c r="K4" s="11" t="inlineStr">
-        <is>
-          <t>(売上高÷前期売上高)−1。FY28は3シナリオの並列(YoY概念外)につき空白。FY27 Base比でBear-9.7%/Base+12.5%/Bull+40.3%</t>
-        </is>
+      <c r="K4" s="11">
+        <f>(今期売上÷前期売上)−1。FY28 3シナリオはYoY概念外につき空白</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -1586,240 +1590,247 @@
       <c r="K6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>医療・介護クラウドPF事業</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
-        <v>2850</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>3365</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>3583</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>4120</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>4700</v>
-      </c>
-      <c r="G7" s="13" t="n">
-        <v>4300</v>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>5400</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>6800</v>
-      </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="B7" s="7">
+        <f>B8+B9+B10</f>
+        <v/>
+      </c>
+      <c r="C7" s="7">
+        <f>C8+C9+C10</f>
+        <v/>
+      </c>
+      <c r="D7" s="7">
+        <f>D8+D9+D10</f>
+        <v/>
+      </c>
+      <c r="E7" s="7">
+        <f>E8+E9+E10</f>
+        <v/>
+      </c>
+      <c r="F7" s="7">
+        <f>F8+F9+F10</f>
+        <v/>
+      </c>
+      <c r="G7" s="7">
+        <f>G8+G9+G10</f>
+        <v/>
+      </c>
+      <c r="H7" s="7">
+        <f>H8+H9+H10</f>
+        <v/>
+      </c>
+      <c r="I7" s="7">
+        <f>I8+I9+I10</f>
+        <v/>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="K7" s="15" t="inlineStr">
-        <is>
-          <t>yuho開示。FY23は健康寿命延伸込みのため845を控除した値(2,850)を併記。FY26+はクラウド+プラットフォーム+その他で構成し、AI課金でARPU上昇</t>
-        </is>
+      <c r="K7" s="5">
+        <f>カナミッククラウド+プラットフォーム+その他(クラウドPF内)。yuho開示と一致</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　カナミッククラウドサービス</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="13" t="n">
         <v>2402</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="13" t="n">
         <v>2853</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="13" t="n">
         <v>2997</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="13" t="n">
         <v>3400</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="13" t="n">
         <v>3900</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="13" t="n">
         <v>3600</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="13" t="n">
         <v>4500</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="13" t="n">
         <v>5700</v>
       </c>
-      <c r="J8" s="18" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="K8" s="19" t="inlineStr">
-        <is>
-          <t>ストックビジネス。FY25は前期比+5.1%、FY24は+18.8%(M&amp;A効果)、本ラインがAI課金の主受益</t>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>ストックビジネス。FY25+5.1%実績、FY24+18.8%(M&amp;A)。AI課金の主受益ライン</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　プラットフォームサービス</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="13" t="n">
         <v>300</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="13" t="n">
         <v>424</v>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="13" t="n">
         <v>474</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="13" t="n">
         <v>550</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="13" t="n">
         <v>620</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="13" t="n">
         <v>550</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="13" t="n">
         <v>700</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="13" t="n">
         <v>850</v>
       </c>
-      <c r="J9" s="18" t="inlineStr"/>
-      <c r="K9" s="19" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>HP構築/介護労働安定センター受託/インターネット広告。FY25+11.9%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　その他サービス(クラウドPF事業内)</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　その他サービス(クラウドPF内)</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
         <v>147</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="13" t="n">
         <v>88</v>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="13" t="n">
         <v>112</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="13" t="n">
         <v>170</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="13" t="n">
         <v>180</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="13" t="n">
         <v>150</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="13" t="n">
         <v>200</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="J10" s="18" t="inlineStr"/>
-      <c r="K10" s="19" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr"/>
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>大口顧客向けカスタマイズ開発受託。ボラあり</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>健康寿命延伸事業</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="17" t="n">
         <v>846</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="17" t="n">
         <v>1131</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="17" t="n">
         <v>1188</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="17" t="n">
         <v>1300</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="17" t="n">
         <v>1400</v>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="I11" s="13" t="n">
+      <c r="I11" s="17" t="n">
         <v>1900</v>
       </c>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="J11" s="18" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="K11" s="15" t="inlineStr">
-        <is>
-          <t>アーバンフィット24(2026年2Q末で27店舗)。FY23時点はクラウドPF事業内で開示、FY24以降にセグメント分離</t>
+      <c r="K11" s="19" t="inlineStr">
+        <is>
+          <t>アーバンフィット24(FY25末24店舗→Vision 2035で年4-6店舗増想定)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>ソリューション開発事業</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="17" t="n">
         <v>51</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="17" t="n">
         <v>512</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="17" t="n">
         <v>730</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="17" t="n">
         <v>930</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="17" t="n">
         <v>1000</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="G12" s="17" t="n">
         <v>800</v>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="17" t="n">
         <v>1100</v>
       </c>
-      <c r="I12" s="13" t="n">
+      <c r="I12" s="17" t="n">
         <v>1400</v>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="18" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-      <c r="K12" s="15" t="inlineStr">
-        <is>
-          <t>Ruby開発(2023/8連結)+TWM(2025/2連結)。FY24+904%/FY25+42.6%。海外展開でも寄与</t>
+      <c r="K12" s="19" t="inlineStr">
+        <is>
+          <t>Ruby開発(2023/8連結)+TWM(2025/2連結)。FY25+42.6%</t>
         </is>
       </c>
     </row>
@@ -1833,43 +1844,43 @@
       <c r="K14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>有料ユーザーID数 (期末、人)</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="n">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>有料ユーザーID数(期末、人)</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
         <v>155516</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="17" t="n">
         <v>191813</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="17" t="n">
         <v>221822</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="17" t="n">
         <v>240000</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="17" t="n">
         <v>260000</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="17" t="n">
         <v>260000</v>
       </c>
-      <c r="H15" s="13" t="n">
+      <c r="H15" s="17" t="n">
         <v>280000</v>
       </c>
-      <c r="I15" s="13" t="n">
+      <c r="I15" s="17" t="n">
         <v>310000</v>
       </c>
-      <c r="J15" s="14" t="inlineStr">
+      <c r="J15" s="18" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>決算説明資料1-8。FY23/9~FY25/9実績。FY26末はFY26-2Q時点247,836→+8%伸び想定。Base CAGR+9%/Bear+6%/Bull+12%</t>
+      <c r="K15" s="19" t="inlineStr">
+        <is>
+          <t>決算説明資料1-8。FY26末はFY26-2Q時点247,836→+8%伸び想定。Base CAGR+9%</t>
         </is>
       </c>
     </row>
@@ -1880,72 +1891,69 @@
         </is>
       </c>
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="9" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>0.082</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>0.241</v>
-      </c>
+      <c r="C16" s="9">
+        <f>C15/B15-1</f>
+        <v/>
+      </c>
+      <c r="D16" s="9">
+        <f>D15/C15-1</f>
+        <v/>
+      </c>
+      <c r="E16" s="9">
+        <f>E15/D15-1</f>
+        <v/>
+      </c>
+      <c r="F16" s="9">
+        <f>F15/E15-1</f>
+        <v/>
+      </c>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
       <c r="J16" s="10" t="inlineStr"/>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>FY24/9末+23.3%(M&amp;A効果)、FY25/9末+15.7%。FY26-FY28はストーリーmd</t>
-        </is>
+      <c r="K16" s="11">
+        <f>(今期ユーザー÷前期ユーザー)−1。FY28 3シナリオはYoY概念外につき空白</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>クラウドPF+ソリューション 月額ARPU (円)</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>クラウドPF+ソリューション 月額ARPU(円)</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
         <v>1350</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="17" t="n">
         <v>1500</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="17" t="n">
         <v>1600</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="17" t="n">
         <v>1660</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="17" t="n">
         <v>1750</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="17" t="n">
         <v>1560</v>
       </c>
-      <c r="H17" s="13" t="n">
+      <c r="H17" s="17" t="n">
         <v>1850</v>
       </c>
-      <c r="I17" s="13" t="n">
+      <c r="I17" s="17" t="n">
         <v>2100</v>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="18" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="K17" s="15" t="inlineStr">
-        <is>
-          <t>(クラウドPF+ソリューション売上) ÷ 有料ユーザー数(年央概算) ÷ 12。FY28はストーリーmd前提。AI課金浸透がドライバー</t>
+      <c r="K17" s="19" t="inlineStr">
+        <is>
+          <t>(クラウドPF+ソリューション)÷ユーザー数(年央)÷12 から逆算。AI課金がドライバー</t>
         </is>
       </c>
     </row>
@@ -1956,768 +1964,811 @@
         </is>
       </c>
       <c r="B18" s="9" t="n"/>
-      <c r="C18" s="9" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>-0.024</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>0.313</v>
-      </c>
+      <c r="C18" s="9">
+        <f>C17/B17-1</f>
+        <v/>
+      </c>
+      <c r="D18" s="9">
+        <f>D17/C17-1</f>
+        <v/>
+      </c>
+      <c r="E18" s="9">
+        <f>E17/D17-1</f>
+        <v/>
+      </c>
+      <c r="F18" s="9">
+        <f>F17/E17-1</f>
+        <v/>
+      </c>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
       <c r="J18" s="10" t="inlineStr"/>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>FY28 BaseはAI課金浸透25-30%でARPU+15.8%、BullはAI浸透40%超でARPU+31%超</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="K18" s="11">
+        <f>(今期ARPU÷前期ARPU)−1。FY28 BaseはAI課金浸透25-30%でARPU+15.6%、Bull 40%超で+31%超</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>検算: ユーザー×ARPU×12 (百万円)</t>
+        </is>
+      </c>
+      <c r="B19" s="7">
+        <f>B15*B17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="C19" s="7">
+        <f>C15*C17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="D19" s="7">
+        <f>D15*D17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="E19" s="7">
+        <f>E15*E17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="F19" s="7">
+        <f>F15*F17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="G19" s="7">
+        <f>G15*G17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="H19" s="7">
+        <f>H15*H17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="I19" s="7">
+        <f>I15*I17*12/1000000</f>
+        <v/>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="5">
+        <f>有料ユーザー × ARPU × 12 ÷ 1,000,000。クラウドPF+ソリューション売上と概ね一致を確認</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">  ▽ AI課金浸透(変曲点ドライバー)</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr"/>
-      <c r="K20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　AI機能浸透率 (有料IDの%)</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="n">
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　AI機能浸透率(有料IDの%)</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="20" t="n">
+      <c r="C22" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="20" t="n">
+      <c r="D22" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="E21" s="20" t="n">
+      <c r="E22" s="20" t="n">
         <v>0.05</v>
       </c>
-      <c r="F21" s="20" t="n">
+      <c r="F22" s="20" t="n">
         <v>0.15</v>
       </c>
-      <c r="G21" s="20" t="n">
+      <c r="G22" s="20" t="n">
         <v>0.1</v>
       </c>
-      <c r="H21" s="20" t="n">
+      <c r="H22" s="20" t="n">
         <v>0.27</v>
       </c>
-      <c r="I21" s="20" t="n">
+      <c r="I22" s="20" t="n">
         <v>0.42</v>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr">
-        <is>
-          <t>FY26から課金開始(AI100-Vision)。Base FY28で25-30%浸透、Bull 40%超。2027年改定で加算要件化なら非線形</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　AI機能 平均月額単価 (円)</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n">
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>FY26課金開始(AI100-Vision)。Base FY28で25-30%、Bull 40%超。2027改定で加算要件化なら非線形</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　AI機能 平均月額単価(円)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+      <c r="E23" s="13" t="n">
         <v>800</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F23" s="13" t="n">
         <v>900</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G23" s="13" t="n">
         <v>700</v>
       </c>
-      <c r="H22" s="17" t="n">
+      <c r="H23" s="13" t="n">
         <v>1000</v>
       </c>
-      <c r="I22" s="17" t="n">
+      <c r="I23" s="13" t="n">
         <v>1200</v>
       </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr">
-        <is>
-          <t>未開示。月額500-1,500円とストーリーmd記載。Base 1,000円/Bear 700/Bull 1,200で置く</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　AI課金 ARPU寄与 (円/月、ブレンド)</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="21" t="n">
+      <c r="K23" s="15" t="inlineStr">
+        <is>
+          <t>未開示。ストーリーmdで月額500-1,500円帯。Base 1,000円で置く</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　AI課金 ARPU寄与(円/月、ブレンド)</t>
+        </is>
+      </c>
+      <c r="B24" s="21">
+        <f>IFERROR(B22*B23,0)</f>
+        <v/>
+      </c>
+      <c r="C24" s="21">
+        <f>IFERROR(C22*C23,0)</f>
+        <v/>
+      </c>
+      <c r="D24" s="21">
+        <f>IFERROR(D22*D23,0)</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>IFERROR(E22*E23,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>IFERROR(F22*F23,0)</f>
+        <v/>
+      </c>
+      <c r="G24" s="21">
+        <f>IFERROR(G22*G23,0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="21">
+        <f>IFERROR(H22*H23,0)</f>
+        <v/>
+      </c>
+      <c r="I24" s="21">
+        <f>IFERROR(I22*I23,0)</f>
+        <v/>
+      </c>
+      <c r="J24" s="10" t="inlineStr"/>
+      <c r="K24" s="11">
+        <f>AI浸透率 × AI平均単価。Base FY28: 27%×1,000=270円が既存ARPUに上乗せ</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ▽ 健康寿命延伸サブドライバー</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　アーバンフィット 店舗数(期末)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>24</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>35</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>32</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="I27" s="13" t="n">
+        <v>42</v>
+      </c>
+      <c r="J27" s="14" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="K27" s="15" t="inlineStr">
+        <is>
+          <t>2026/3末で27店舗(2026年5月時点)。Vision 2035で年4-6店舗増</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1店舗あたり年商(百万円)</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n">
+        <v>65</v>
+      </c>
+      <c r="C28" s="22" t="n">
+        <v>57</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>49</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>43</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="H28" s="22" t="n">
+        <v>44</v>
+      </c>
+      <c r="I28" s="22" t="n">
+        <v>45</v>
+      </c>
+      <c r="J28" s="14" t="inlineStr"/>
+      <c r="K28" s="15" t="inlineStr">
+        <is>
+          <t>健康寿命延伸事業売上÷期中平均店舗数。新規出店は当初低稼働、徐々に45百万へ収斂</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>【粗利】</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　粗利率</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n">
+        <v>0.6925</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <v>0.6428</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I31" s="20" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J31" s="14" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="K31" s="15" t="inlineStr">
+        <is>
+          <t>FY23-25は actual_粗利/actual_売上 から計算。FY24はM&amp;A連結で一時悪化。AI限界利益≒100%で漸増</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>売上総利益</t>
+        </is>
+      </c>
+      <c r="B32" s="7">
+        <f>B3*B31</f>
+        <v/>
+      </c>
+      <c r="C32" s="7">
+        <f>C3*C31</f>
+        <v/>
+      </c>
+      <c r="D32" s="7">
+        <f>D3*D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="7">
+        <f>E3*E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="7">
+        <f>F3*F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="7">
+        <f>G3*G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="7">
+        <f>H3*H31</f>
+        <v/>
+      </c>
+      <c r="I32" s="7">
+        <f>I3*I31</f>
+        <v/>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="5">
+        <f>売上高 × 粗利率</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>売上原価</t>
+        </is>
+      </c>
+      <c r="B33" s="7">
+        <f>B3-B32</f>
+        <v/>
+      </c>
+      <c r="C33" s="7">
+        <f>C3-C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="7">
+        <f>D3-D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="7">
+        <f>E3-E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="7">
+        <f>F3-F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="7">
+        <f>G3-G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="7">
+        <f>H3-H32</f>
+        <v/>
+      </c>
+      <c r="I33" s="7">
+        <f>I3-I32</f>
+        <v/>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="5">
+        <f>売上高 − 売上総利益</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>【販管費】</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>販管費 合計</t>
+        </is>
+      </c>
+      <c r="B36" s="7">
+        <f>B32-B48</f>
+        <v/>
+      </c>
+      <c r="C36" s="7">
+        <f>C32-C48</f>
+        <v/>
+      </c>
+      <c r="D36" s="7">
+        <f>D32-D48</f>
+        <v/>
+      </c>
+      <c r="E36" s="7">
+        <f>E32-E48</f>
+        <v/>
+      </c>
+      <c r="F36" s="7">
+        <f>F32-F48</f>
+        <v/>
+      </c>
+      <c r="G36" s="7">
+        <f>G32-G48</f>
+        <v/>
+      </c>
+      <c r="H36" s="7">
+        <f>H32-H48</f>
+        <v/>
+      </c>
+      <c r="I36" s="7">
+        <f>I32-I48</f>
+        <v/>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="5">
+        <f>売上総利益 − 営業利益 (=粗利−営利)。SG&amp;A項目はSUM参考のみで強制せず</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　従業員給料</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>353</v>
+      </c>
+      <c r="C37" s="13" t="n">
+        <v>381</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>486</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>580</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>670</v>
+      </c>
+      <c r="G37" s="13" t="n">
+        <v>620</v>
+      </c>
+      <c r="H37" s="13" t="n">
+        <v>760</v>
+      </c>
+      <c r="I37" s="13" t="n">
+        <v>950</v>
+      </c>
+      <c r="J37" s="14" t="inlineStr"/>
+      <c r="K37" s="15" t="inlineStr">
+        <is>
+          <t>yuho販管費注記。FY25+27.6%は新規連結とTWM連結(2025/2)。SaaS人件費は売上に劣後成長</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　役員報酬</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>241</v>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>251</v>
+      </c>
+      <c r="D38" s="13" t="n">
+        <v>256</v>
+      </c>
+      <c r="E38" s="13" t="n">
+        <v>270</v>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>285</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>280</v>
+      </c>
+      <c r="H38" s="13" t="n">
+        <v>295</v>
+      </c>
+      <c r="I38" s="13" t="n">
+        <v>310</v>
+      </c>
+      <c r="J38" s="14" t="inlineStr"/>
+      <c r="K38" s="15" t="inlineStr">
+        <is>
+          <t>yuho販管費注記。安定推移</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　地代家賃</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="C39" s="13" t="n">
+        <v>92</v>
+      </c>
+      <c r="D39" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E39" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="G39" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="I39" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="J39" s="14" t="inlineStr"/>
+      <c r="K39" s="15" t="inlineStr">
+        <is>
+          <t>本社+営業所(7拠点)。FY25は再配置で減</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　法定福利費</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>82</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>125</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>120</v>
+      </c>
+      <c r="H40" s="13" t="n">
+        <v>140</v>
+      </c>
+      <c r="I40" s="13" t="n">
+        <v>170</v>
+      </c>
+      <c r="J40" s="14" t="inlineStr"/>
+      <c r="K40" s="15" t="inlineStr">
+        <is>
+          <t>従業員給料に概ね連動</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　賞与引当金繰入額</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="C41" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="F23" s="21" t="n">
-        <v>135</v>
-      </c>
-      <c r="G23" s="21" t="n">
+      <c r="D41" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="E41" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F41" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="H23" s="21" t="n">
-        <v>270</v>
-      </c>
-      <c r="I23" s="21" t="n">
-        <v>504</v>
-      </c>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>浸透率 × 平均単価。Base FY28: 27%×1,000=270円が既存ARPUに上乗せ</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ▽ 健康寿命延伸サブドライバー</t>
-        </is>
-      </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="5" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　アーバンフィット 店舗数 (期末)</t>
-        </is>
-      </c>
-      <c r="B26" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="C26" s="22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D26" s="22" t="n">
-        <v>24</v>
-      </c>
-      <c r="E26" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="F26" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>32</v>
-      </c>
-      <c r="H26" s="22" t="n">
-        <v>36</v>
-      </c>
-      <c r="I26" s="22" t="n">
-        <v>42</v>
-      </c>
-      <c r="J26" s="18" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="K26" s="19" t="inlineStr">
-        <is>
-          <t>2026/3末で27店舗(2026年5月時点)。Vision 2035ベースで年4-6店舗増想定</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　1店舗あたり年商 (百万円)</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="n">
+      <c r="G41" s="13" t="n">
         <v>65</v>
       </c>
-      <c r="C27" s="23" t="n">
-        <v>57</v>
-      </c>
-      <c r="D27" s="23" t="n">
-        <v>49</v>
-      </c>
-      <c r="E27" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="F27" s="23" t="n">
-        <v>43</v>
-      </c>
-      <c r="G27" s="23" t="n">
+      <c r="H41" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="I41" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J41" s="14" t="inlineStr"/>
+      <c r="K41" s="15" t="inlineStr">
+        <is>
+          <t>業績連動。OPM拡大局面で増額</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　減価償却費(販管費分)</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
         <v>44</v>
       </c>
-      <c r="H27" s="23" t="n">
-        <v>44</v>
-      </c>
-      <c r="I27" s="23" t="n">
-        <v>45</v>
-      </c>
-      <c r="J27" s="18" t="inlineStr"/>
-      <c r="K27" s="19" t="inlineStr">
-        <is>
-          <t>健康寿命延伸事業売上 ÷ 期中平均店舗数。新規出店で当初は低稼働、徐々に45百万へ収斂</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>【粗利】</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>売上原価</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n">
-        <v>1152</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>1935</v>
-      </c>
-      <c r="D30" s="7" t="n">
-        <v>1964</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>2223</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>2448</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>2308</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>2673</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>3131</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>連結P&amp;L(FY23-25実績)。FY26+は売上×(1-粗利率)。FY24は新規連結(Ruby/アーバンフィット)で粗利率低下</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>売上総利益</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="n">
-        <v>2594</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>3072</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>3536</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>4128</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>4752</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>4193</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>5427</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>6969</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr"/>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
-          <t>連結P&amp;L。FY26+は売上×粗利率</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　粗利率</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="n">
-        <v>0.6919999999999999</v>
-      </c>
-      <c r="C32" s="20" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="D32" s="20" t="n">
-        <v>0.643</v>
-      </c>
-      <c r="E32" s="20" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="G32" s="20" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="H32" s="20" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I32" s="20" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="J32" s="18" t="inlineStr"/>
-      <c r="K32" s="19" t="inlineStr">
-        <is>
-          <t>FY23 69.2%→FY24 61.4%(M&amp;Aで一時悪化)→FY25 64.3%回復→AI課金限界利益≈100%で漸増</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>【販管費】</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr"/>
-      <c r="K34" s="5" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>販管費 合計</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>1498</v>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>1633</v>
-      </c>
-      <c r="D35" s="7" t="n">
-        <v>1930</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <v>2078</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>2376</v>
-      </c>
-      <c r="G35" s="7" t="n">
-        <v>2243</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>2677</v>
-      </c>
-      <c r="I35" s="7" t="n">
-        <v>3232</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr"/>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>連結P&amp;L(FY23-25実績)。FY26+は粗利−営利。営業利益率目標から逆算</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　従業員給料</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n">
-        <v>353</v>
-      </c>
-      <c r="C36" s="17" t="n">
-        <v>381</v>
-      </c>
-      <c r="D36" s="17" t="n">
-        <v>486</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>580</v>
-      </c>
-      <c r="F36" s="17" t="n">
-        <v>670</v>
-      </c>
-      <c r="G36" s="17" t="n">
-        <v>620</v>
-      </c>
-      <c r="H36" s="17" t="n">
-        <v>760</v>
-      </c>
-      <c r="I36" s="17" t="n">
-        <v>950</v>
-      </c>
-      <c r="J36" s="18" t="inlineStr"/>
-      <c r="K36" s="19" t="inlineStr">
-        <is>
-          <t>yuho販管費注記。FY25+27.6%は新規連結とTWM連結(2025/2)。SaaS人件費は売上に劣後成長</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　役員報酬</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="n">
-        <v>241</v>
-      </c>
-      <c r="C37" s="17" t="n">
-        <v>251</v>
-      </c>
-      <c r="D37" s="17" t="n">
-        <v>256</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>270</v>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>285</v>
-      </c>
-      <c r="G37" s="17" t="n">
-        <v>280</v>
-      </c>
-      <c r="H37" s="17" t="n">
-        <v>295</v>
-      </c>
-      <c r="I37" s="17" t="n">
-        <v>310</v>
-      </c>
-      <c r="J37" s="18" t="inlineStr"/>
-      <c r="K37" s="19" t="inlineStr">
-        <is>
-          <t>yuho販管費注記。FY24+4%、FY25+2.3%。安定推移</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　地代家賃</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="C38" s="17" t="n">
-        <v>92</v>
-      </c>
-      <c r="D38" s="17" t="n">
-        <v>85</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>90</v>
-      </c>
-      <c r="F38" s="17" t="n">
-        <v>95</v>
-      </c>
-      <c r="G38" s="17" t="n">
-        <v>95</v>
-      </c>
-      <c r="H38" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="I38" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="J38" s="18" t="inlineStr"/>
-      <c r="K38" s="19" t="inlineStr">
-        <is>
-          <t>本社+営業所(7拠点)。FY25は減(再配置)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　法定福利費</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n">
-        <v>77</v>
-      </c>
-      <c r="C39" s="17" t="n">
-        <v>82</v>
-      </c>
-      <c r="D39" s="17" t="n">
-        <v>99</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>110</v>
-      </c>
-      <c r="F39" s="17" t="n">
-        <v>125</v>
-      </c>
-      <c r="G39" s="17" t="n">
-        <v>120</v>
-      </c>
-      <c r="H39" s="17" t="n">
-        <v>140</v>
-      </c>
-      <c r="I39" s="17" t="n">
-        <v>170</v>
-      </c>
-      <c r="J39" s="18" t="inlineStr"/>
-      <c r="K39" s="19" t="inlineStr">
-        <is>
-          <t>従業員給料に概ね連動</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　賞与引当金繰入額</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="n">
-        <v>37</v>
-      </c>
-      <c r="C40" s="17" t="n">
-        <v>40</v>
-      </c>
-      <c r="D40" s="17" t="n">
-        <v>51</v>
-      </c>
-      <c r="E40" s="17" t="n">
+      <c r="C42" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="D42" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="E42" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="F42" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="G42" s="13" t="n">
+        <v>55</v>
+      </c>
+      <c r="H42" s="13" t="n">
         <v>60</v>
       </c>
-      <c r="F40" s="17" t="n">
+      <c r="I42" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="G40" s="17" t="n">
-        <v>65</v>
-      </c>
-      <c r="H40" s="17" t="n">
-        <v>80</v>
-      </c>
-      <c r="I40" s="17" t="n">
-        <v>100</v>
-      </c>
-      <c r="J40" s="18" t="inlineStr"/>
-      <c r="K40" s="19" t="inlineStr">
-        <is>
-          <t>業績連動。OPM拡大局面で増額</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　減価償却費</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="n">
-        <v>44</v>
-      </c>
-      <c r="C41" s="17" t="n">
-        <v>46</v>
-      </c>
-      <c r="D41" s="17" t="n">
-        <v>47</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>50</v>
-      </c>
-      <c r="F41" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="G41" s="17" t="n">
-        <v>55</v>
-      </c>
-      <c r="H41" s="17" t="n">
-        <v>60</v>
-      </c>
-      <c r="I41" s="17" t="n">
-        <v>70</v>
-      </c>
-      <c r="J41" s="18" t="inlineStr"/>
-      <c r="K41" s="19" t="inlineStr">
-        <is>
-          <t>販管費分のみ。連結全体の減価償却費はFY25で332百万(B/S)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="J42" s="14" t="inlineStr"/>
+      <c r="K42" s="15" t="inlineStr">
+        <is>
+          <t>販管費分のみ。連結全体はB/Sの減価償却費を別途参照</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　貸倒引当金繰入額</t>
         </is>
       </c>
-      <c r="B42" s="17" t="n">
+      <c r="B43" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="C42" s="17" t="n">
+      <c r="C43" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="D42" s="17" t="n">
+      <c r="D43" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="17" t="n">
+      <c r="E43" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="F42" s="17" t="n">
+      <c r="F43" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="G42" s="17" t="n">
+      <c r="G43" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="H42" s="17" t="n">
+      <c r="H43" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I42" s="17" t="n">
+      <c r="I43" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="J42" s="18" t="inlineStr"/>
-      <c r="K42" s="19" t="inlineStr">
+      <c r="J43" s="14" t="inlineStr"/>
+      <c r="K43" s="15" t="inlineStr">
         <is>
           <t>据え置き(過去レンジ1-6百万)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　その他販管費</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="n">
-        <v>657</v>
-      </c>
-      <c r="C43" s="17" t="n">
-        <v>735</v>
-      </c>
-      <c r="D43" s="17" t="n">
-        <v>905</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>915</v>
-      </c>
-      <c r="F43" s="17" t="n">
-        <v>1073</v>
-      </c>
-      <c r="G43" s="17" t="n">
-        <v>1005</v>
-      </c>
-      <c r="H43" s="17" t="n">
-        <v>1239</v>
-      </c>
-      <c r="I43" s="17" t="n">
-        <v>1519</v>
-      </c>
-      <c r="J43" s="18" t="inlineStr"/>
-      <c r="K43" s="19" t="inlineStr">
-        <is>
-          <t>販管費合計から上記内訳を差引いた残余(外注費/広告/業務委託等)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　その他販管費(差分)</t>
+        </is>
+      </c>
+      <c r="B44" s="21">
+        <f>B36-B37-B38-B39-B40-B41-B42-B43</f>
+        <v/>
+      </c>
+      <c r="C44" s="21">
+        <f>C36-C37-C38-C39-C40-C41-C42-C43</f>
+        <v/>
+      </c>
+      <c r="D44" s="21">
+        <f>D36-D37-D38-D39-D40-D41-D42-D43</f>
+        <v/>
+      </c>
+      <c r="E44" s="21">
+        <f>E36-E37-E38-E39-E40-E41-E42-E43</f>
+        <v/>
+      </c>
+      <c r="F44" s="21">
+        <f>F36-F37-F38-F39-F40-F41-F42-F43</f>
+        <v/>
+      </c>
+      <c r="G44" s="21">
+        <f>G36-G37-G38-G39-G40-G41-G42-G43</f>
+        <v/>
+      </c>
+      <c r="H44" s="21">
+        <f>H36-H37-H38-H39-H40-H41-H42-H43</f>
+        <v/>
+      </c>
+      <c r="I44" s="21">
+        <f>I36-I37-I38-I39-I40-I41-I42-I43</f>
+        <v/>
+      </c>
+      <c r="J44" s="10" t="inlineStr"/>
+      <c r="K44" s="11">
+        <f>販管費合計 − 上記7項目のSUM。外注費/広告/業務委託等</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>【利益】</t>
         </is>
       </c>
-      <c r="J45" s="4" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>営業利益</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="n">
-        <v>1096</v>
-      </c>
-      <c r="C46" s="7" t="n">
-        <v>1439</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>1607</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>2050</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>2376</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>1950</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>2750</v>
-      </c>
-      <c r="I46" s="7" t="n">
-        <v>3737</v>
-      </c>
       <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>連結P&amp;L(FY23-25実績)。FY26会社予想2,050。FY27-FY28シナリオはストーリーmd</t>
-        </is>
-      </c>
+      <c r="K46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　営業利益率</t>
         </is>
       </c>
       <c r="B47" s="20" t="n">
-        <v>0.293</v>
+        <v>0.2926</v>
       </c>
       <c r="C47" s="20" t="n">
-        <v>0.287</v>
+        <v>0.2874</v>
       </c>
       <c r="D47" s="20" t="n">
-        <v>0.292</v>
+        <v>0.2922</v>
       </c>
       <c r="E47" s="20" t="n">
-        <v>0.323</v>
+        <v>0.3228</v>
       </c>
       <c r="F47" s="20" t="n">
         <v>0.33</v>
@@ -2731,86 +2782,93 @@
       <c r="I47" s="20" t="n">
         <v>0.37</v>
       </c>
-      <c r="J47" s="18" t="inlineStr">
+      <c r="J47" s="14" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="K47" s="19" t="inlineStr">
-        <is>
-          <t>FY25 29.2%→FY26予32.3%。Vision 2035で2030年33-35%目標。Base FY28 34%は妥当、AI限界利益反映</t>
+      <c r="K47" s="15" t="inlineStr">
+        <is>
+          <t>FY23-25は actual_営利/actual_売上。Vision 2035で2030年33-35%目標、FY28 Base 34%は妥当</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>経常利益</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>1107</v>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>1448</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1613</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>2055</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>2380</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>1955</v>
-      </c>
-      <c r="H48" s="7" t="n">
-        <v>2755</v>
-      </c>
-      <c r="I48" s="7" t="n">
-        <v>3745</v>
+          <t>営業利益</t>
+        </is>
+      </c>
+      <c r="B48" s="7">
+        <f>B3*B47</f>
+        <v/>
+      </c>
+      <c r="C48" s="7">
+        <f>C3*C47</f>
+        <v/>
+      </c>
+      <c r="D48" s="7">
+        <f>D3*D47</f>
+        <v/>
+      </c>
+      <c r="E48" s="7">
+        <f>E3*E47</f>
+        <v/>
+      </c>
+      <c r="F48" s="7">
+        <f>F3*F47</f>
+        <v/>
+      </c>
+      <c r="G48" s="7">
+        <f>G3*G47</f>
+        <v/>
+      </c>
+      <c r="H48" s="7">
+        <f>H3*H47</f>
+        <v/>
+      </c>
+      <c r="I48" s="7">
+        <f>I3*I47</f>
+        <v/>
       </c>
       <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>連結P&amp;L(FY23-25実績)。営業外損益は小幅。FY26+は営利+5百万で簡略</t>
-        </is>
+      <c r="K48" s="5">
+        <f>売上高 × 営業利益率</f>
+        <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　営業外損益(純)</t>
         </is>
       </c>
-      <c r="B49" s="17" t="n">
+      <c r="B49" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="C49" s="17" t="n">
+      <c r="C49" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="D49" s="17" t="n">
+      <c r="D49" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E49" s="17" t="n">
+      <c r="E49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="F49" s="17" t="n">
+      <c r="F49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="G49" s="17" t="n">
+      <c r="G49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="H49" s="17" t="n">
+      <c r="H49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="I49" s="17" t="n">
+      <c r="I49" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="J49" s="18" t="inlineStr"/>
-      <c r="K49" s="19" t="inlineStr">
+      <c r="J49" s="14" t="inlineStr"/>
+      <c r="K49" s="15" t="inlineStr">
         <is>
           <t>受取利息/手数料等。安定して+5〜10百万円</t>
         </is>
@@ -2819,91 +2877,105 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>税金等調整前純利益</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="n">
-        <v>1104</v>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>1352</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>1613</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>2055</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>2380</v>
-      </c>
-      <c r="G50" s="7" t="n">
-        <v>1955</v>
-      </c>
-      <c r="H50" s="7" t="n">
-        <v>2755</v>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>3745</v>
+          <t>経常利益</t>
+        </is>
+      </c>
+      <c r="B50" s="7">
+        <f>B48+B49</f>
+        <v/>
+      </c>
+      <c r="C50" s="7">
+        <f>C48+C49</f>
+        <v/>
+      </c>
+      <c r="D50" s="7">
+        <f>D48+D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="7">
+        <f>E48+E49</f>
+        <v/>
+      </c>
+      <c r="F50" s="7">
+        <f>F48+F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="7">
+        <f>G48+G49</f>
+        <v/>
+      </c>
+      <c r="H50" s="7">
+        <f>H48+H49</f>
+        <v/>
+      </c>
+      <c r="I50" s="7">
+        <f>I48+I49</f>
+        <v/>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
-      <c r="K50" s="5" t="inlineStr">
-        <is>
-          <t>FY24は特別損失(減損96+移転7)で経常から減少。FY26+は特益・特損ゼロ想定</t>
-        </is>
+      <c r="K50" s="5">
+        <f>営業利益 + 営業外損益(純)</f>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>法人税等</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="n">
-        <v>341</v>
-      </c>
-      <c r="C51" s="7" t="n">
-        <v>432</v>
-      </c>
-      <c r="D51" s="7" t="n">
-        <v>501</v>
-      </c>
-      <c r="E51" s="7" t="n">
-        <v>617</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>714</v>
-      </c>
-      <c r="G51" s="7" t="n">
-        <v>587</v>
-      </c>
-      <c r="H51" s="7" t="n">
-        <v>827</v>
-      </c>
-      <c r="I51" s="7" t="n">
-        <v>1124</v>
+          <t>税金等調整前純利益</t>
+        </is>
+      </c>
+      <c r="B51" s="7">
+        <f>B50</f>
+        <v/>
+      </c>
+      <c r="C51" s="7">
+        <f>C50</f>
+        <v/>
+      </c>
+      <c r="D51" s="7">
+        <f>D50</f>
+        <v/>
+      </c>
+      <c r="E51" s="7">
+        <f>E50</f>
+        <v/>
+      </c>
+      <c r="F51" s="7">
+        <f>F50</f>
+        <v/>
+      </c>
+      <c r="G51" s="7">
+        <f>G50</f>
+        <v/>
+      </c>
+      <c r="H51" s="7">
+        <f>H50</f>
+        <v/>
+      </c>
+      <c r="I51" s="7">
+        <f>I50</f>
+        <v/>
       </c>
       <c r="J51" s="4" t="inlineStr"/>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>実効税率を乗じた値</t>
-        </is>
+      <c r="K51" s="5">
+        <f>経常利益 (FY24は特別損失104百万で経常から減少、参考値1,352)</f>
+        <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">　実効税率</t>
         </is>
       </c>
       <c r="B52" s="20" t="n">
-        <v>0.309</v>
+        <v>0.3088</v>
       </c>
       <c r="C52" s="20" t="n">
-        <v>0.32</v>
+        <v>0.3198</v>
       </c>
       <c r="D52" s="20" t="n">
-        <v>0.311</v>
+        <v>0.3108</v>
       </c>
       <c r="E52" s="20" t="n">
         <v>0.3</v>
@@ -2920,409 +2992,472 @@
       <c r="I52" s="20" t="n">
         <v>0.3</v>
       </c>
-      <c r="J52" s="18" t="inlineStr"/>
-      <c r="K52" s="19" t="inlineStr">
-        <is>
-          <t>FY23-25実績30-32%。法定実効税率約30%。FY26+は30%で固定</t>
+      <c r="J52" s="14" t="inlineStr"/>
+      <c r="K52" s="15" t="inlineStr">
+        <is>
+          <t>FY23-25 actual 30.9-32.0%。法定実効税率約30%。FY26+は30%固定</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
+          <t>法人税等</t>
+        </is>
+      </c>
+      <c r="B53" s="7">
+        <f>B51*B52</f>
+        <v/>
+      </c>
+      <c r="C53" s="7">
+        <f>C51*C52</f>
+        <v/>
+      </c>
+      <c r="D53" s="7">
+        <f>D51*D52</f>
+        <v/>
+      </c>
+      <c r="E53" s="7">
+        <f>E51*E52</f>
+        <v/>
+      </c>
+      <c r="F53" s="7">
+        <f>F51*F52</f>
+        <v/>
+      </c>
+      <c r="G53" s="7">
+        <f>G51*G52</f>
+        <v/>
+      </c>
+      <c r="H53" s="7">
+        <f>H51*H52</f>
+        <v/>
+      </c>
+      <c r="I53" s="7">
+        <f>I51*I52</f>
+        <v/>
+      </c>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="5">
+        <f>税前 × 実効税率</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>親会社株主帰属純利益</t>
         </is>
       </c>
-      <c r="B53" s="7" t="n">
-        <v>763</v>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>920</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>1112</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>1437</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>1666</v>
-      </c>
-      <c r="G53" s="7" t="n">
-        <v>1369</v>
-      </c>
-      <c r="H53" s="7" t="n">
-        <v>1929</v>
-      </c>
-      <c r="I53" s="7" t="n">
-        <v>2622</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr"/>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>連結P&amp;L。FY26会社予想は1,370(28.5円)、ストーリー値とほぼ一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="B54" s="7">
+        <f>B51-B53</f>
+        <v/>
+      </c>
+      <c r="C54" s="7">
+        <f>C51-C53</f>
+        <v/>
+      </c>
+      <c r="D54" s="7">
+        <f>D51-D53</f>
+        <v/>
+      </c>
+      <c r="E54" s="7">
+        <f>E51-E53</f>
+        <v/>
+      </c>
+      <c r="F54" s="7">
+        <f>F51-F53</f>
+        <v/>
+      </c>
+      <c r="G54" s="7">
+        <f>G51-G53</f>
+        <v/>
+      </c>
+      <c r="H54" s="7">
+        <f>H51-H53</f>
+        <v/>
+      </c>
+      <c r="I54" s="7">
+        <f>I51-I53</f>
+        <v/>
+      </c>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="5">
+        <f>税前 − 法人税等。FY26会社予想は1,370(28.5円)、ほぼ一致</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>【補助KPI: SaaS指標】</t>
         </is>
       </c>
-      <c r="J55" s="4" t="inlineStr"/>
-      <c r="K55" s="5" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>導入地域数 (期末)</t>
-        </is>
-      </c>
-      <c r="B56" s="24" t="n">
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="5" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>導入地域数(期末)</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
         <v>1270</v>
       </c>
-      <c r="C56" s="24" t="n">
+      <c r="C57" s="17" t="n">
         <v>1320</v>
       </c>
-      <c r="D56" s="24" t="n">
+      <c r="D57" s="17" t="n">
         <v>1397</v>
       </c>
-      <c r="E56" s="24" t="n">
+      <c r="E57" s="17" t="n">
         <v>1440</v>
       </c>
-      <c r="F56" s="24" t="n">
+      <c r="F57" s="17" t="n">
         <v>1490</v>
       </c>
-      <c r="G56" s="24" t="n">
+      <c r="G57" s="17" t="n">
         <v>1460</v>
       </c>
-      <c r="H56" s="24" t="n">
+      <c r="H57" s="17" t="n">
         <v>1510</v>
       </c>
-      <c r="I56" s="24" t="n">
+      <c r="I57" s="17" t="n">
         <v>1580</v>
       </c>
-      <c r="J56" s="14" t="inlineStr"/>
-      <c r="K56" s="15" t="inlineStr">
+      <c r="J57" s="18" t="inlineStr"/>
+      <c r="K57" s="19" t="inlineStr">
         <is>
           <t>決算説明資料1-7。中学校区(人口3万人圏)単位。FY26 2Q時点1,420地域</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="12" t="inlineStr">
-        <is>
-          <t>無料ユーザーID数 (期末)</t>
-        </is>
-      </c>
-      <c r="B57" s="13" t="n">
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>無料ユーザーID数(期末)</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
         <v>86760</v>
       </c>
-      <c r="C57" s="13" t="n">
+      <c r="C58" s="17" t="n">
         <v>101309</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D58" s="17" t="n">
         <v>117497</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E58" s="17" t="n">
         <v>135000</v>
       </c>
-      <c r="F57" s="13" t="n">
+      <c r="F58" s="17" t="n">
         <v>152000</v>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="G58" s="17" t="n">
         <v>145000</v>
       </c>
-      <c r="H57" s="13" t="n">
+      <c r="H58" s="17" t="n">
         <v>158000</v>
       </c>
-      <c r="I57" s="13" t="n">
+      <c r="I58" s="17" t="n">
         <v>175000</v>
       </c>
-      <c r="J57" s="14" t="inlineStr"/>
-      <c r="K57" s="15" t="inlineStr">
-        <is>
-          <t>決算説明資料1-8。無料→有料転換のパイプライン。介護情報基盤稼働で増加加速可能性</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>ユーザーID合計</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="n">
-        <v>242276</v>
-      </c>
-      <c r="C58" s="7" t="n">
-        <v>293122</v>
-      </c>
-      <c r="D58" s="7" t="n">
-        <v>339319</v>
-      </c>
-      <c r="E58" s="7" t="n">
-        <v>375000</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>412000</v>
-      </c>
-      <c r="G58" s="7" t="n">
-        <v>405000</v>
-      </c>
-      <c r="H58" s="7" t="n">
-        <v>438000</v>
-      </c>
-      <c r="I58" s="7" t="n">
-        <v>485000</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr"/>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>有料+無料。FY26 2Q時点で376,972</t>
+      <c r="J58" s="18" t="inlineStr"/>
+      <c r="K58" s="19" t="inlineStr">
+        <is>
+          <t>無料→有料転換のパイプライン。介護情報基盤稼働で増加加速可能性</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n">
-        <v>1140</v>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>1740</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>1939</v>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>2900</v>
-      </c>
-      <c r="G59" s="7" t="n">
-        <v>2400</v>
-      </c>
-      <c r="H59" s="7" t="n">
-        <v>3300</v>
-      </c>
-      <c r="I59" s="7" t="n">
-        <v>4400</v>
+          <t>ユーザーID合計</t>
+        </is>
+      </c>
+      <c r="B59" s="7">
+        <f>B15+B58</f>
+        <v/>
+      </c>
+      <c r="C59" s="7">
+        <f>C15+C58</f>
+        <v/>
+      </c>
+      <c r="D59" s="7">
+        <f>D15+D58</f>
+        <v/>
+      </c>
+      <c r="E59" s="7">
+        <f>E15+E58</f>
+        <v/>
+      </c>
+      <c r="F59" s="7">
+        <f>F15+F58</f>
+        <v/>
+      </c>
+      <c r="G59" s="7">
+        <f>G15+G58</f>
+        <v/>
+      </c>
+      <c r="H59" s="7">
+        <f>H15+H58</f>
+        <v/>
+      </c>
+      <c r="I59" s="7">
+        <f>I15+I58</f>
+        <v/>
       </c>
       <c r="J59" s="4" t="inlineStr"/>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>営業利益+減価償却費(連結全体)。FY25実は1,939、FY26会社予想は2,500</t>
-        </is>
+      <c r="K59" s="5">
+        <f>有料ユーザーID + 無料ユーザーID</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>EBITDA(連結減価償却足戻し)</t>
+        </is>
+      </c>
+      <c r="B60" s="7">
+        <f>B48+B61</f>
+        <v/>
+      </c>
+      <c r="C60" s="7">
+        <f>C48+C61</f>
+        <v/>
+      </c>
+      <c r="D60" s="7">
+        <f>D48+D61</f>
+        <v/>
+      </c>
+      <c r="E60" s="7">
+        <f>E48+E61</f>
+        <v/>
+      </c>
+      <c r="F60" s="7">
+        <f>F48+F61</f>
+        <v/>
+      </c>
+      <c r="G60" s="7">
+        <f>G48+G61</f>
+        <v/>
+      </c>
+      <c r="H60" s="7">
+        <f>H48+H61</f>
+        <v/>
+      </c>
+      <c r="I60" s="7">
+        <f>I48+I61</f>
+        <v/>
+      </c>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="5">
+        <f>営業利益 + 連結減価償却費</f>
+        <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>連結減価償却費(全体、参考)</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n">
+        <v>268</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>301</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>332</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="F61" s="17" t="n">
+        <v>524</v>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>450</v>
+      </c>
+      <c r="H61" s="17" t="n">
+        <v>550</v>
+      </c>
+      <c r="I61" s="17" t="n">
+        <v>663</v>
+      </c>
+      <c r="J61" s="18" t="inlineStr"/>
+      <c r="K61" s="19" t="inlineStr">
+        <is>
+          <t>B/S(連結CF表)。販管費分+原価分の合計。FY25は332百万</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>【株価・PER感応度】</t>
         </is>
       </c>
-      <c r="J61" s="4" t="inlineStr"/>
-      <c r="K61" s="5" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
-        <is>
-          <t>発行済株式数 (千株、期末)</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="D62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="E62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="G62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="H62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="I62" s="13" t="n">
-        <v>48132</v>
-      </c>
-      <c r="J62" s="14" t="inlineStr"/>
-      <c r="K62" s="15" t="inlineStr">
-        <is>
-          <t>yuho開示。直近5年48,132千株で据置(自己株消却・新株発行なし)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="6" t="inlineStr">
-        <is>
-          <t>EPS (円)</t>
-        </is>
-      </c>
-      <c r="B63" s="25" t="n">
-        <v>16.08</v>
-      </c>
-      <c r="C63" s="25" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="D63" s="25" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="E63" s="25" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="F63" s="25" t="n">
-        <v>34.62</v>
-      </c>
-      <c r="G63" s="25" t="n">
-        <v>28.45</v>
-      </c>
-      <c r="H63" s="25" t="n">
-        <v>40.08</v>
-      </c>
-      <c r="I63" s="25" t="n">
-        <v>54.48</v>
-      </c>
       <c r="J63" s="4" t="inlineStr"/>
-      <c r="K63" s="5" t="inlineStr">
-        <is>
-          <t>純利益÷発行済株式数。FY23-25はyuho開示と一致。FY28 Base 40.0/Bull 54.4はストーリーmd</t>
-        </is>
-      </c>
+      <c r="K63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">　想定PER ベスト(Bull水準)</t>
-        </is>
-      </c>
-      <c r="B64" s="23" t="n"/>
-      <c r="C64" s="23" t="n"/>
-      <c r="D64" s="23" t="n"/>
-      <c r="E64" s="23" t="n"/>
-      <c r="F64" s="23" t="n"/>
-      <c r="G64" s="23" t="n"/>
-      <c r="H64" s="23" t="n"/>
-      <c r="I64" s="23" t="n">
-        <v>22</v>
+          <t>発行済株式数(千株)</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="C64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="F64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="G64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="H64" s="17" t="n">
+        <v>48132</v>
+      </c>
+      <c r="I64" s="17" t="n">
+        <v>48132</v>
       </c>
       <c r="J64" s="18" t="inlineStr"/>
       <c r="K64" s="19" t="inlineStr">
         <is>
-          <t>Bullシナリオ:AI浸透確認でプレミアム。情報通信SaaS OPM30%超で18-25倍が相場、+α</t>
+          <t>yuho開示。直近5年48,132千株で据置(自己株消却・新株発行なし)。EPS算定上は期中平均≒47,460(自己株差)だが簡略化のため期末で固定</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　想定PER ノーマル(Base水準)</t>
-        </is>
-      </c>
-      <c r="B65" s="23" t="n"/>
-      <c r="C65" s="23" t="n"/>
-      <c r="D65" s="23" t="n"/>
-      <c r="E65" s="23" t="n"/>
-      <c r="F65" s="23" t="n"/>
-      <c r="G65" s="23" t="n"/>
-      <c r="H65" s="23" t="n">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>EPS(円)</t>
+        </is>
+      </c>
+      <c r="B65" s="23">
+        <f>B54*1000/B64</f>
+        <v/>
+      </c>
+      <c r="C65" s="23">
+        <f>C54*1000/C64</f>
+        <v/>
+      </c>
+      <c r="D65" s="23">
+        <f>D54*1000/D64</f>
+        <v/>
+      </c>
+      <c r="E65" s="23">
+        <f>E54*1000/E64</f>
+        <v/>
+      </c>
+      <c r="F65" s="23">
+        <f>F54*1000/F64</f>
+        <v/>
+      </c>
+      <c r="G65" s="23">
+        <f>G54*1000/G64</f>
+        <v/>
+      </c>
+      <c r="H65" s="23">
+        <f>H54*1000/H64</f>
+        <v/>
+      </c>
+      <c r="I65" s="23">
+        <f>I54*1000/I64</f>
+        <v/>
+      </c>
+      <c r="J65" s="4" t="inlineStr"/>
+      <c r="K65" s="5">
+        <f>純利益 × 1,000 ÷ 発行済株式数(千株)。FY28 Base 40.1円 ≒ ストーリー40.0円</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　想定PER ベスト(Bull)</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="22" t="n"/>
+      <c r="D66" s="22" t="n"/>
+      <c r="E66" s="22" t="n"/>
+      <c r="F66" s="22" t="n"/>
+      <c r="G66" s="22" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="J66" s="14" t="inlineStr"/>
+      <c r="K66" s="15" t="inlineStr">
+        <is>
+          <t>Bullシナリオ:AI浸透確認でプレミアム。SaaS OPM30%超で18-25倍が相場、+α</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　想定PER ノーマル(Base)</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="n"/>
+      <c r="C67" s="22" t="n"/>
+      <c r="D67" s="22" t="n"/>
+      <c r="E67" s="22" t="n"/>
+      <c r="F67" s="22" t="n"/>
+      <c r="G67" s="22" t="n"/>
+      <c r="H67" s="22" t="n">
         <v>19</v>
       </c>
-      <c r="I65" s="23" t="n"/>
-      <c r="J65" s="18" t="inlineStr"/>
-      <c r="K65" s="19" t="inlineStr">
+      <c r="I67" s="22" t="n"/>
+      <c r="J67" s="14" t="inlineStr"/>
+      <c r="K67" s="15" t="inlineStr">
         <is>
           <t>Baseシナリオ:現状PER(19.3倍)維持。SaaS中央値かつカナミック直近の典型水準</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　想定PER ワースト(Bear水準)</t>
-        </is>
-      </c>
-      <c r="B66" s="23" t="n"/>
-      <c r="C66" s="23" t="n"/>
-      <c r="D66" s="23" t="n"/>
-      <c r="E66" s="23" t="n"/>
-      <c r="F66" s="23" t="n"/>
-      <c r="G66" s="23" t="n">
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　想定PER ワースト(Bear)</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="n"/>
+      <c r="C68" s="22" t="n"/>
+      <c r="D68" s="22" t="n"/>
+      <c r="E68" s="22" t="n"/>
+      <c r="F68" s="22" t="n"/>
+      <c r="G68" s="22" t="n">
         <v>16</v>
       </c>
-      <c r="H66" s="23" t="n"/>
-      <c r="I66" s="23" t="n"/>
-      <c r="J66" s="18" t="inlineStr"/>
-      <c r="K66" s="19" t="inlineStr">
+      <c r="H68" s="22" t="n"/>
+      <c r="I68" s="22" t="n"/>
+      <c r="J68" s="14" t="inlineStr"/>
+      <c r="K68" s="15" t="inlineStr">
         <is>
           <t>Bearシナリオ:AI浸透遅延でディスカウント。過去レンジ下限14.9倍に若干上乗せ</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>目標株価 Bull (円)</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="n"/>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="7" t="n"/>
-      <c r="I67" s="7" t="n">
-        <v>1199</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr"/>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>FY28 Bull EPS 54.48 × 22倍 = 1,199円(現値+118%、ストーリー1,197と一致)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>目標株価 Base (円)</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
-      <c r="E68" s="7" t="n"/>
-      <c r="F68" s="7" t="n"/>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="7" t="n">
-        <v>762</v>
-      </c>
-      <c r="I68" s="7" t="n"/>
-      <c r="J68" s="4" t="inlineStr"/>
-      <c r="K68" s="5" t="inlineStr">
-        <is>
-          <t>FY28 Base EPS 40.08 × 19倍 = 762円(現値+38%、ストーリー760と一致)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>目標株価 Bear (円)</t>
+          <t>目標株価 Bull(円)</t>
         </is>
       </c>
       <c r="B69" s="7" t="n"/>
@@ -3330,339 +3465,327 @@
       <c r="D69" s="7" t="n"/>
       <c r="E69" s="7" t="n"/>
       <c r="F69" s="7" t="n"/>
-      <c r="G69" s="7" t="n">
-        <v>455</v>
-      </c>
+      <c r="G69" s="7" t="n"/>
       <c r="H69" s="7" t="n"/>
-      <c r="I69" s="7" t="n"/>
+      <c r="I69" s="7">
+        <f>I65*I66</f>
+        <v/>
+      </c>
       <c r="J69" s="4" t="inlineStr"/>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>FY28 Bear EPS 28.45 × 16倍 = 455円(現値-17%、ストーリー454と一致)</t>
-        </is>
+      <c r="K69" s="5">
+        <f>FY28 Bull EPS × Bull想定PER。Bull EPS 54.5 × 22倍 ≒ 1,199円(現値+118%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>目標株価 Base(円)</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n"/>
+      <c r="C70" s="7" t="n"/>
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="7" t="n"/>
+      <c r="F70" s="7" t="n"/>
+      <c r="G70" s="7" t="n"/>
+      <c r="H70" s="7">
+        <f>H65*H67</f>
+        <v/>
+      </c>
+      <c r="I70" s="7" t="n"/>
+      <c r="J70" s="4" t="inlineStr"/>
+      <c r="K70" s="5">
+        <f>FY28 Base EPS × Base想定PER。Base EPS 40.1 × 19倍 ≒ 762円(現値+38%)</f>
+        <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>目標株価 Bear(円)</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n"/>
+      <c r="C71" s="7" t="n"/>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
+      <c r="F71" s="7" t="n"/>
+      <c r="G71" s="7">
+        <f>G65*G68</f>
+        <v/>
+      </c>
+      <c r="H71" s="7" t="n"/>
+      <c r="I71" s="7" t="n"/>
+      <c r="J71" s="4" t="inlineStr"/>
+      <c r="K71" s="5">
+        <f>FY28 Bear EPS × Bear想定PER。Bear EPS 28.5 × 16倍 ≒ 455円(現値-17%)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>【「織り込み済み?」反論】</t>
         </is>
       </c>
-      <c r="J71" s="4" t="inlineStr"/>
-      <c r="K71" s="5" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="inlineStr">
-        <is>
-          <t>時価総額 (百万円、現値据置)</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
+      <c r="J73" s="4" t="inlineStr"/>
+      <c r="K73" s="5" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="inlineStr">
+        <is>
+          <t>時価総額(百万円、現値据置)</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="C72" s="13" t="n">
+      <c r="C74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="F72" s="13" t="n">
+      <c r="F74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="G72" s="13" t="n">
+      <c r="G74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="H72" s="13" t="n">
+      <c r="H74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="I72" s="13" t="n">
+      <c r="I74" s="17" t="n">
         <v>26473</v>
       </c>
-      <c r="J72" s="14" t="inlineStr"/>
-      <c r="K72" s="15" t="inlineStr">
-        <is>
-          <t>2026年5月13日株価550円 × 48,132千株 = 26,473百万円で全期間固定</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　連結純利益 Base (再掲)</t>
-        </is>
-      </c>
-      <c r="B73" s="21" t="n">
-        <v>763</v>
-      </c>
-      <c r="C73" s="21" t="n">
-        <v>920</v>
-      </c>
-      <c r="D73" s="21" t="n">
-        <v>1112</v>
-      </c>
-      <c r="E73" s="21" t="n">
-        <v>1437</v>
-      </c>
-      <c r="F73" s="21" t="n">
-        <v>1666</v>
-      </c>
-      <c r="G73" s="21" t="n">
-        <v>1369</v>
-      </c>
-      <c r="H73" s="21" t="n">
-        <v>1929</v>
-      </c>
-      <c r="I73" s="21" t="n">
-        <v>2622</v>
-      </c>
-      <c r="J73" s="10" t="inlineStr"/>
-      <c r="K73" s="11" t="inlineStr">
-        <is>
-          <t>上記P&amp;Lより再掲</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　時価総額据置PER (倍)</t>
-        </is>
-      </c>
-      <c r="B74" s="26" t="n">
-        <v>34.7</v>
-      </c>
-      <c r="C74" s="26" t="n">
-        <v>28.8</v>
-      </c>
-      <c r="D74" s="26" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E74" s="26" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="F74" s="26" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="G74" s="26" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="H74" s="26" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="I74" s="26" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J74" s="10" t="inlineStr"/>
-      <c r="K74" s="11" t="inlineStr">
-        <is>
-          <t>時価総額 ÷ 純利益。株価変わらず利益増ならPERが機械的に低下→現値に純利益成長は織込まれていない</t>
-        </is>
+      <c r="J74" s="18" t="inlineStr"/>
+      <c r="K74" s="19" t="inlineStr">
+        <is>
+          <t>2026/5/13株価550円 × 48,132千株 = 26,473百万円で全期間固定</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　連結純利益 Base(再掲)</t>
+        </is>
+      </c>
+      <c r="B75" s="21">
+        <f>B54</f>
+        <v/>
+      </c>
+      <c r="C75" s="21">
+        <f>C54</f>
+        <v/>
+      </c>
+      <c r="D75" s="21">
+        <f>D54</f>
+        <v/>
+      </c>
+      <c r="E75" s="21">
+        <f>E54</f>
+        <v/>
+      </c>
+      <c r="F75" s="21">
+        <f>F54</f>
+        <v/>
+      </c>
+      <c r="G75" s="21">
+        <f>G54</f>
+        <v/>
+      </c>
+      <c r="H75" s="21">
+        <f>H54</f>
+        <v/>
+      </c>
+      <c r="I75" s="21">
+        <f>I54</f>
+        <v/>
+      </c>
+      <c r="J75" s="10" t="inlineStr"/>
+      <c r="K75" s="11">
+        <f>親会社株主帰属純利益(上記P&amp;Lより再掲)</f>
+        <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>【ピア比較 (PER)】※純粋同業未上場、多軸選定</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="inlineStr"/>
-      <c r="K76" s="5" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="12" t="inlineStr">
-        <is>
-          <t>カナミック (3939) 現状PER</t>
-        </is>
-      </c>
-      <c r="B77" s="27" t="n"/>
-      <c r="C77" s="27" t="n"/>
-      <c r="D77" s="27" t="n"/>
-      <c r="E77" s="27" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F77" s="27" t="n"/>
-      <c r="G77" s="27" t="n"/>
-      <c r="H77" s="27" t="n"/>
-      <c r="I77" s="27" t="n"/>
-      <c r="J77" s="14" t="inlineStr"/>
-      <c r="K77" s="15" t="inlineStr">
-        <is>
-          <t>株価550円 ÷ FY26予EPS 28.46円 = 19.3倍(2026年5月13日時点)</t>
-        </is>
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　時価総額据置PER(倍)</t>
+        </is>
+      </c>
+      <c r="B76" s="24">
+        <f>B74/B54</f>
+        <v/>
+      </c>
+      <c r="C76" s="24">
+        <f>C74/C54</f>
+        <v/>
+      </c>
+      <c r="D76" s="24">
+        <f>D74/D54</f>
+        <v/>
+      </c>
+      <c r="E76" s="24">
+        <f>E74/E54</f>
+        <v/>
+      </c>
+      <c r="F76" s="24">
+        <f>F74/F54</f>
+        <v/>
+      </c>
+      <c r="G76" s="24">
+        <f>G74/G54</f>
+        <v/>
+      </c>
+      <c r="H76" s="24">
+        <f>H74/H54</f>
+        <v/>
+      </c>
+      <c r="I76" s="24">
+        <f>I74/I54</f>
+        <v/>
+      </c>
+      <c r="J76" s="10" t="inlineStr"/>
+      <c r="K76" s="11">
+        <f>時価総額 ÷ 純利益。株価据置で利益増ならPER低下→現値に純利益成長は織込まれていない</f>
+        <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ピア① エス・エム・エス (2175)</t>
-        </is>
-      </c>
-      <c r="B78" s="23" t="n"/>
-      <c r="C78" s="23" t="n"/>
-      <c r="D78" s="23" t="n"/>
-      <c r="E78" s="23" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="F78" s="23" t="n"/>
-      <c r="G78" s="23" t="n"/>
-      <c r="H78" s="23" t="n"/>
-      <c r="I78" s="23" t="n"/>
-      <c r="J78" s="18" t="inlineStr"/>
-      <c r="K78" s="19" t="inlineStr">
-        <is>
-          <t>医療介護領域のヘルスケアSaaS+人材プラットフォーム。軸:同業界(介護DX)。直近実績PERをIR確認推奨</t>
-        </is>
-      </c>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>【ピア比較(PER) ※純粋同業未上場、多軸選定】</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">　ピア② ラクス (3923)</t>
-        </is>
-      </c>
-      <c r="B79" s="23" t="n"/>
-      <c r="C79" s="23" t="n"/>
-      <c r="D79" s="23" t="n"/>
-      <c r="E79" s="23" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="F79" s="23" t="n"/>
-      <c r="G79" s="23" t="n"/>
-      <c r="H79" s="23" t="n"/>
-      <c r="I79" s="23" t="n"/>
+          <t>カナミック(3939) 現状PER</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="n"/>
+      <c r="C79" s="25" t="n"/>
+      <c r="D79" s="25" t="n"/>
+      <c r="E79" s="25" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F79" s="25" t="n"/>
+      <c r="G79" s="25" t="n"/>
+      <c r="H79" s="25" t="n"/>
+      <c r="I79" s="25" t="n"/>
       <c r="J79" s="18" t="inlineStr"/>
       <c r="K79" s="19" t="inlineStr">
         <is>
-          <t>中小事業者向け低単価SaaS(楽楽精算等)。軸:ビジネスモデル類似(課金1,500円帯×多数の小口顧客)。高成長SaaSプレミアム参考</t>
+          <t>株価550円 ÷ FY26予EPS 28.46円 ≒ 19.3倍(2026/5/13)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ピア③ JMDC (4483)</t>
-        </is>
-      </c>
-      <c r="B80" s="23" t="n"/>
-      <c r="C80" s="23" t="n"/>
-      <c r="D80" s="23" t="n"/>
-      <c r="E80" s="23" t="inlineStr">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ピア① エス・エム・エス(2175)</t>
+        </is>
+      </c>
+      <c r="B80" s="13" t="n"/>
+      <c r="C80" s="13" t="n"/>
+      <c r="D80" s="13" t="n"/>
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="F80" s="23" t="n"/>
-      <c r="G80" s="23" t="n"/>
-      <c r="H80" s="23" t="n"/>
-      <c r="I80" s="23" t="n"/>
-      <c r="J80" s="18" t="inlineStr"/>
-      <c r="K80" s="19" t="inlineStr">
-        <is>
-          <t>医療データプラットフォーム。軸:制度受益(医療DX政策・基盤)+データMoat。直近FY26予想ベースPERをIR確認推奨</t>
+      <c r="F80" s="13" t="n"/>
+      <c r="G80" s="13" t="n"/>
+      <c r="H80" s="13" t="n"/>
+      <c r="I80" s="13" t="n"/>
+      <c r="J80" s="14" t="inlineStr"/>
+      <c r="K80" s="15" t="inlineStr">
+        <is>
+          <t>医療介護領域のヘルスケアSaaS+人材PF。軸:同業界(介護DX)。直近実績PERをIR確認推奨</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　ピア中央値(参考レンジ20-30倍)</t>
-        </is>
-      </c>
-      <c r="B81" s="23" t="n"/>
-      <c r="C81" s="23" t="n"/>
-      <c r="D81" s="23" t="n"/>
-      <c r="E81" s="23" t="inlineStr">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ピア② ラクス(3923)</t>
+        </is>
+      </c>
+      <c r="B81" s="13" t="n"/>
+      <c r="C81" s="13" t="n"/>
+      <c r="D81" s="13" t="n"/>
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>TODO</t>
         </is>
       </c>
-      <c r="F81" s="23" t="n"/>
-      <c r="G81" s="23" t="n"/>
-      <c r="H81" s="23" t="n"/>
-      <c r="I81" s="23" t="n"/>
-      <c r="J81" s="18" t="inlineStr"/>
-      <c r="K81" s="19" t="inlineStr">
-        <is>
-          <t>プライム情報通信SaaS(OPM30%超・増益率20%超)のPER相場18-25倍を参考。実数値は要IR確認</t>
+      <c r="F81" s="13" t="n"/>
+      <c r="G81" s="13" t="n"/>
+      <c r="H81" s="13" t="n"/>
+      <c r="I81" s="13" t="n"/>
+      <c r="J81" s="14" t="inlineStr"/>
+      <c r="K81" s="15" t="inlineStr">
+        <is>
+          <t>中小事業者向け低単価SaaS(楽楽精算等)。軸:ビジネスモデル類似(低単価高浸透)。高成長SaaSプレミアム参考</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ピア③ JMDC(4483)</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="13" t="n"/>
+      <c r="I82" s="13" t="n"/>
+      <c r="J82" s="14" t="inlineStr"/>
+      <c r="K82" s="15" t="inlineStr">
+        <is>
+          <t>医療データプラットフォーム。軸:制度受益(医療DX政策・基盤)+データMoat</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>【仮定根拠の要約】</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="5" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
-        <is>
-          <t>業績タイプ判定</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
-      <c r="E84" s="7" t="n"/>
-      <c r="F84" s="7" t="n"/>
-      <c r="G84" s="7" t="n"/>
-      <c r="H84" s="7" t="n"/>
-      <c r="I84" s="7" t="n"/>
-      <c r="J84" s="4" t="inlineStr"/>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>SaaS型(ユーザー数×ARPU×12)。AlbaLink型(1人粗利×人数)+セグメント型のハイブリッド。主因数: 有料ID数とARPU</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>ストーリー核心</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="7" t="n"/>
-      <c r="G85" s="7" t="n"/>
-      <c r="H85" s="7" t="n"/>
-      <c r="I85" s="7" t="n"/>
-      <c r="J85" s="4" t="inlineStr"/>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>既存22万有料ID×AI課金で獲得コストゼロのARPU階段上昇。2027年改定+介護情報基盤稼働の3つが2026-27に重なる構造変化</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>最大の独立変数</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="7" t="n"/>
-      <c r="F86" s="7" t="n"/>
-      <c r="G86" s="7" t="n"/>
-      <c r="H86" s="7" t="n"/>
-      <c r="I86" s="7" t="n"/>
-      <c r="J86" s="4" t="inlineStr"/>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>(1)AI機能浸透率 (2)AI平均単価 (3)有料ユーザーCAGR。この3つでBear-Bullレンジが決まる</t>
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　ピア中央値(参考)</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="n"/>
+      <c r="C83" s="13" t="n"/>
+      <c r="D83" s="13" t="n"/>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="n"/>
+      <c r="G83" s="13" t="n"/>
+      <c r="H83" s="13" t="n"/>
+      <c r="I83" s="13" t="n"/>
+      <c r="J83" s="14" t="inlineStr"/>
+      <c r="K83" s="15" t="inlineStr">
+        <is>
+          <t>プライム情報通信SaaS(OPM30%超・増益率20%超)のPER相場18-25倍を参考</t>
         </is>
       </c>
     </row>
